--- a/data/trans_bre/P6905-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 42,86</t>
+          <t>-3,31; 44,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 42,55</t>
+          <t>-3,52; 42,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 39,58</t>
+          <t>-3,02; 38,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 34,14</t>
+          <t>-21,96; 36,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 134,42</t>
+          <t>-7,28; 144,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 119,18</t>
+          <t>-5,48; 123,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 166,01</t>
+          <t>-9,15; 163,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 153,64</t>
+          <t>-41,98; 170,04</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 24,44</t>
+          <t>-15,33; 21,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 11,71</t>
+          <t>-26,63; 11,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 29,79</t>
+          <t>-6,49; 29,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,19; 54,7</t>
+          <t>14,0; 55,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 147,35</t>
+          <t>-51,05; 136,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 57,82</t>
+          <t>-74,41; 55,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 116,79</t>
+          <t>-15,76; 121,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 675,88</t>
+          <t>28,92; 605,26</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,61; 16,83</t>
+          <t>-29,53; 16,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 25,82</t>
+          <t>-28,57; 23,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 28,26</t>
+          <t>-17,89; 26,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 26,48</t>
+          <t>5,0; 26,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 132,39</t>
+          <t>-84,05; 126,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 162,48</t>
+          <t>-76,97; 237,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,13; —</t>
+          <t>-16,43; —</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 32,47</t>
+          <t>-13,14; 33,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 52,91</t>
+          <t>8,44; 51,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 35,27</t>
+          <t>-12,59; 36,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 9,97</t>
+          <t>-52,16; 11,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 199,65</t>
+          <t>-41,5; 218,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 469,28</t>
+          <t>16,35; 552,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 136,39</t>
+          <t>-21,87; 142,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,67; 32,44</t>
+          <t>-88,27; 42,53</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 73,8</t>
+          <t>-8,49; 70,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 78,59</t>
+          <t>5,62; 78,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 63,14</t>
+          <t>-26,51; 65,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 18,03</t>
+          <t>-19,09; 20,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 650,91</t>
+          <t>-35,54; 600,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 1315,68</t>
+          <t>10,76; 1307,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 297,0</t>
+          <t>-43,88; 371,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 46,32</t>
+          <t>-13,03; 47,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 27,69</t>
+          <t>-19,07; 29,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 71,51</t>
+          <t>-8,88; 73,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 22,36</t>
+          <t>-12,22; 22,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 132,19</t>
+          <t>-21,95; 143,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,05; 186,27</t>
+          <t>-71,7; 226,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 242,19</t>
+          <t>-46,99; 239,88</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 25,24</t>
+          <t>-10,55; 25,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 33,08</t>
+          <t>-5,0; 33,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 38,33</t>
+          <t>4,64; 37,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 28,65</t>
+          <t>0,34; 29,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 96,38</t>
+          <t>-27,54; 106,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 169,58</t>
+          <t>-14,85; 182,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,82; 352,66</t>
+          <t>18,18; 337,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 159,72</t>
+          <t>0,8; 172,52</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 33,29</t>
+          <t>0,32; 33,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 44,94</t>
+          <t>2,27; 45,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 14,61</t>
+          <t>-29,49; 16,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 26,83</t>
+          <t>-12,14; 30,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,45; 151,34</t>
+          <t>0,72; 159,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 671,79</t>
+          <t>1,18; 655,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-84,61; 90,48</t>
+          <t>-84,7; 113,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 194,27</t>
+          <t>-45,22; 226,88</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,85</t>
+          <t>3,01; 18,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,34; 23,46</t>
+          <t>5,79; 22,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,94; 22,74</t>
+          <t>5,18; 22,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 17,46</t>
+          <t>-0,18; 17,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,35; 70,17</t>
+          <t>8,28; 67,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,45; 104,06</t>
+          <t>19,1; 100,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,03; 96,42</t>
+          <t>17,0; 94,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 91,13</t>
+          <t>-0,15; 89,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6905-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>11,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 44,48</t>
+          <t>-5,51; 44,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 42,64</t>
+          <t>-4,67; 42,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 38,98</t>
+          <t>-1,12; 38,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 36,27</t>
+          <t>-16,68; 36,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 144,91</t>
+          <t>-10,29; 149,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 123,11</t>
+          <t>-7,51; 117,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 163,35</t>
+          <t>-3,63; 167,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 170,04</t>
+          <t>-38,39; 218,76</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36,6</t>
+          <t>30,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>187,82%</t>
+          <t>131,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 21,65</t>
+          <t>-15,62; 22,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 11,88</t>
+          <t>-26,27; 9,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 29,48</t>
+          <t>-5,93; 31,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,0; 55,26</t>
+          <t>11,11; 49,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 136,13</t>
+          <t>-49,69; 167,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,41; 55,36</t>
+          <t>-73,56; 43,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 121,61</t>
+          <t>-15,12; 124,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,92; 605,26</t>
+          <t>24,09; 408,61</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,51</t>
+          <t>15,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>386,66%</t>
+          <t>404,31%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 16,47</t>
+          <t>-28,64; 15,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 23,66</t>
+          <t>-31,6; 22,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 26,35</t>
+          <t>-19,21; 26,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 26,44</t>
+          <t>4,37; 26,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-84,05; 126,01</t>
+          <t>-83,17; 129,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-76,97; 237,65</t>
+          <t>-81,11; 144,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,43; —</t>
+          <t>22,82; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-14,93</t>
+          <t>-6,86</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-37,63%</t>
+          <t>-13,84%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 33,29</t>
+          <t>-14,3; 29,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 51,54</t>
+          <t>7,81; 52,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 36,73</t>
+          <t>-10,76; 38,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 11,05</t>
+          <t>-28,64; 14,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,5; 218,8</t>
+          <t>-47,9; 174,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 552,92</t>
+          <t>15,27; 528,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 142,97</t>
+          <t>-21,53; 145,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,27; 42,53</t>
+          <t>-46,3; 44,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-7,18%</t>
+          <t>-11,61%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 70,68</t>
+          <t>-8,93; 74,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 78,31</t>
+          <t>6,04; 78,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 65,27</t>
+          <t>-29,64; 64,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 20,08</t>
+          <t>-19,07; 17,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 600,85</t>
+          <t>-29,77; 663,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 1307,52</t>
+          <t>17,65; 1419,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,88; 371,93</t>
+          <t>-52,73; 306,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 670,73</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,5</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 47,31</t>
+          <t>-11,83; 44,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 29,96</t>
+          <t>-19,74; 27,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 73,48</t>
+          <t>-8,74; 73,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 22,61</t>
+          <t>-12,83; 23,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 143,74</t>
+          <t>-21,84; 116,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,7; 226,33</t>
+          <t>-71,03; 187,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1677,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 239,88</t>
+          <t>-47,04; 256,52</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,09</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 25,98</t>
+          <t>-10,33; 24,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 33,26</t>
+          <t>-5,44; 36,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 37,44</t>
+          <t>6,04; 37,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 29,87</t>
+          <t>-2,85; 25,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 106,41</t>
+          <t>-26,91; 96,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 182,45</t>
+          <t>-16,98; 197,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,18; 337,38</t>
+          <t>22,78; 371,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 172,52</t>
+          <t>-8,78; 142,27</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>-5,41</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>-21,08%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 33,56</t>
+          <t>-0,38; 34,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 45,34</t>
+          <t>1,2; 46,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 16,4</t>
+          <t>-28,4; 15,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 30,78</t>
+          <t>-18,76; 11,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 159,71</t>
+          <t>-1,8; 171,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 655,9</t>
+          <t>-9,29; 764,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-84,7; 113,96</t>
+          <t>-79,76; 98,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 226,88</t>
+          <t>-56,29; 76,24</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 18,75</t>
+          <t>2,9; 19,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,79; 22,76</t>
+          <t>6,83; 24,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,18; 22,52</t>
+          <t>5,42; 22,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 17,74</t>
+          <t>1,56; 15,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,28; 67,27</t>
+          <t>8,99; 71,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,1; 100,31</t>
+          <t>22,47; 105,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,0; 94,61</t>
+          <t>16,84; 95,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 89,57</t>
+          <t>4,93; 71,85</t>
         </is>
       </c>
     </row>
